--- a/artfynd/A 52048-2019 artfynd.xlsx
+++ b/artfynd/A 52048-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52048-2019 artfynd.xlsx
+++ b/artfynd/A 52048-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2118,6 +2118,125 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>125979915</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57453</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stenkärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575368</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6370573</v>
+      </c>
+      <c r="S13" t="n">
+        <v>50</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kristdala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>23:10</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jan Nilsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jan Nilsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52048-2019 artfynd.xlsx
+++ b/artfynd/A 52048-2019 artfynd.xlsx
@@ -2123,7 +2123,7 @@
         <v>125979915</v>
       </c>
       <c r="B13" t="n">
-        <v>57453</v>
+        <v>57454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52048-2019 artfynd.xlsx
+++ b/artfynd/A 52048-2019 artfynd.xlsx
@@ -2123,7 +2123,7 @@
         <v>125979915</v>
       </c>
       <c r="B13" t="n">
-        <v>57454</v>
+        <v>57458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52048-2019 artfynd.xlsx
+++ b/artfynd/A 52048-2019 artfynd.xlsx
@@ -2123,7 +2123,7 @@
         <v>125979915</v>
       </c>
       <c r="B13" t="n">
-        <v>57458</v>
+        <v>57459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
